--- a/data/trans_camb/P16A_n_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 15,68</t>
+          <t>5,88; 14,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,97</t>
+          <t>0,86; 9,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,79; 19,51</t>
+          <t>10,7; 19,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,08; 20,61</t>
+          <t>11,02; 20,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 15,74</t>
+          <t>6,05; 15,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 18,92</t>
+          <t>4,73; 18,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 16,51</t>
+          <t>9,42; 16,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,96</t>
+          <t>4,46; 11,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,76; 17,91</t>
+          <t>10,49; 18,35</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,03; 101,07</t>
+          <t>30,26; 94,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 64,78</t>
+          <t>4,1; 63,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57,16; 131,04</t>
+          <t>55,17; 128,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,37; 86,21</t>
+          <t>37,85; 86,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,61; 66,38</t>
+          <t>21,26; 67,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,79; 78,85</t>
+          <t>19,42; 78,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,46; 82,1</t>
+          <t>41,33; 81,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 54,01</t>
+          <t>18,92; 54,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,35; 88,4</t>
+          <t>45,97; 91,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 10,21</t>
+          <t>2,32; 9,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,74</t>
+          <t>1,29; 8,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 9,38</t>
+          <t>-8,2; 9,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,08</t>
+          <t>3,97; 12,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,03</t>
+          <t>0,57; 9,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 15,9</t>
+          <t>7,74; 15,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 10,43</t>
+          <t>4,91; 10,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,92</t>
+          <t>2,45; 7,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 10,72</t>
+          <t>-3,66; 10,7</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,99; 60,79</t>
+          <t>11,89; 61,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 52,46</t>
+          <t>6,54; 53,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 54,34</t>
+          <t>-44,17; 51,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 49,07</t>
+          <t>13,13; 48,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 34,12</t>
+          <t>1,75; 35,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,01; 60,14</t>
+          <t>24,45; 59,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,59; 47,37</t>
+          <t>19,64; 49,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 36,27</t>
+          <t>9,77; 36,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 46,95</t>
+          <t>-15,1; 46,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,99</t>
+          <t>1,46; 10,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 8,9</t>
+          <t>0,49; 9,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 19,16</t>
+          <t>8,86; 18,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 12,53</t>
+          <t>2,92; 12,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,35</t>
+          <t>-5,47; 3,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 43,85</t>
+          <t>3,56; 46,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,27</t>
+          <t>3,83; 10,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 5,08</t>
+          <t>-1,34; 5,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 37,31</t>
+          <t>8,45; 37,32</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 69,85</t>
+          <t>8,24; 75,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 63,23</t>
+          <t>2,5; 63,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,13; 128,18</t>
+          <t>47,52; 128,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 43,31</t>
+          <t>8,21; 43,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 15,01</t>
+          <t>-16,6; 14,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 150,55</t>
+          <t>11,28; 156,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,76; 47,04</t>
+          <t>14,48; 45,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 22,77</t>
+          <t>-5,11; 23,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,4; 161,09</t>
+          <t>35,37; 170,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,19; 12,82</t>
+          <t>5,21; 12,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,09</t>
+          <t>3,31; 10,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,4; 18,22</t>
+          <t>10,76; 18,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 13,93</t>
+          <t>5,47; 14,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,72</t>
+          <t>1,16; 9,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 12,56</t>
+          <t>-0,39; 12,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,15</t>
+          <t>6,55; 12,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 9,16</t>
+          <t>3,51; 9,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 14,01</t>
+          <t>6,36; 13,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,39; 79,52</t>
+          <t>27,21; 81,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,49; 62,81</t>
+          <t>16,6; 65,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,24; 113,11</t>
+          <t>53,74; 113,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,31; 46,52</t>
+          <t>16,43; 47,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,64; 31,81</t>
+          <t>3,51; 33,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 41,06</t>
+          <t>0,03; 41,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,22; 50,94</t>
+          <t>24,53; 53,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,62; 38,28</t>
+          <t>13,39; 38,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,39; 58,79</t>
+          <t>25,69; 58,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,04</t>
+          <t>5,76; 9,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 7,53</t>
+          <t>3,58; 7,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,69; 13,37</t>
+          <t>4,11; 13,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,57</t>
+          <t>7,8; 12,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,14</t>
+          <t>2,72; 7,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,81; 24,83</t>
+          <t>8,74; 23,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,69</t>
+          <t>7,51; 10,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,86</t>
+          <t>3,75; 6,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,23; 17,89</t>
+          <t>8,36; 17,13</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>31,84; 60,41</t>
+          <t>31,36; 57,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19,22; 45,27</t>
+          <t>19,65; 44,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27,24; 79,39</t>
+          <t>23,44; 77,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,37; 43,76</t>
+          <t>25,13; 43,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,59; 24,98</t>
+          <t>8,55; 25,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,98; 81,85</t>
+          <t>28,86; 79,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,51; 46,76</t>
+          <t>30,29; 46,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,0; 29,42</t>
+          <t>14,9; 29,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>34,25; 76,79</t>
+          <t>34,48; 72,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,09</t>
+          <t>14,95</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,73</t>
+          <t>15,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,69</t>
+          <t>15,61</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 14,65</t>
+          <t>5,83; 14,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,39</t>
+          <t>0,81; 9,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 19,55</t>
+          <t>10,38; 19,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,02; 20,95</t>
+          <t>10,84; 20,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 15,84</t>
+          <t>5,11; 15,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 18,63</t>
+          <t>11,65; 20,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 16,36</t>
+          <t>9,69; 16,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 11,16</t>
+          <t>4,71; 11,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 18,35</t>
+          <t>12,48; 18,84</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,26; 94,66</t>
+          <t>30,08; 95,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 63,17</t>
+          <t>4,26; 62,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,17; 128,51</t>
+          <t>53,79; 130,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,85; 86,75</t>
+          <t>37,89; 88,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,26; 67,09</t>
+          <t>17,94; 63,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,42; 78,07</t>
+          <t>40,43; 85,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,33; 81,23</t>
+          <t>41,48; 80,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,92; 54,78</t>
+          <t>20,23; 55,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,97; 91,18</t>
+          <t>53,1; 94,87</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,58</t>
+          <t>7,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,56</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>9,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,98</t>
+          <t>2,4; 10,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 8,69</t>
+          <t>1,52; 9,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 9,12</t>
+          <t>4,07; 11,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 12,9</t>
+          <t>4,36; 13,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 9,59</t>
+          <t>0,96; 9,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 15,65</t>
+          <t>7,01; 14,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 10,77</t>
+          <t>4,63; 10,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,98</t>
+          <t>2,12; 8,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 10,7</t>
+          <t>6,7; 12,29</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,89; 61,55</t>
+          <t>12,49; 63,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 53,88</t>
+          <t>7,13; 54,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 51,76</t>
+          <t>20,54; 71,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 48,36</t>
+          <t>14,29; 49,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 35,83</t>
+          <t>3,09; 35,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,45; 59,62</t>
+          <t>22,43; 56,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,64; 49,24</t>
+          <t>18,24; 48,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 36,05</t>
+          <t>8,36; 36,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 46,61</t>
+          <t>26,72; 55,56</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,85</t>
+          <t>13,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,38</t>
+          <t>6,52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,01</t>
+          <t>10,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 10,38</t>
+          <t>1,62; 10,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,07</t>
+          <t>0,8; 8,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 18,49</t>
+          <t>9,57; 18,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 12,78</t>
+          <t>2,76; 12,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 3,95</t>
+          <t>-5,93; 3,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 46,27</t>
+          <t>1,77; 10,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,03</t>
+          <t>3,56; 10,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 5,3</t>
+          <t>-1,79; 5,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,45; 37,32</t>
+          <t>6,72; 13,54</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,24; 75,36</t>
+          <t>8,17; 73,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 63,97</t>
+          <t>4,13; 61,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,52; 128,55</t>
+          <t>51,71; 132,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,21; 43,47</t>
+          <t>8,84; 44,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 14,09</t>
+          <t>-17,29; 14,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,28; 156,77</t>
+          <t>4,98; 38,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,48; 45,19</t>
+          <t>14,15; 47,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 23,97</t>
+          <t>-6,9; 22,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35,37; 170,11</t>
+          <t>26,2; 61,15</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>13,56</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,01</t>
+          <t>11,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 12,9</t>
+          <t>5,37; 12,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,55</t>
+          <t>3,11; 10,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,76; 18,14</t>
+          <t>9,35; 17,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 14,13</t>
+          <t>5,73; 13,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,75</t>
+          <t>1,66; 10,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 12,9</t>
+          <t>6,16; 13,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,55; 12,46</t>
+          <t>6,44; 12,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,1</t>
+          <t>3,17; 9,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,99</t>
+          <t>8,9; 14,27</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,21; 81,07</t>
+          <t>26,48; 77,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,6; 65,97</t>
+          <t>16,16; 64,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53,74; 113,39</t>
+          <t>48,47; 107,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,43; 47,43</t>
+          <t>17,13; 46,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 33,64</t>
+          <t>4,87; 34,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 41,99</t>
+          <t>17,73; 46,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,53; 53,24</t>
+          <t>23,68; 51,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 38,43</t>
+          <t>11,85; 38,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,69; 58,55</t>
+          <t>33,59; 60,95</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>12,16</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,81</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,61</t>
+          <t>5,84; 9,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,29</t>
+          <t>3,64; 7,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,19</t>
+          <t>10,15; 14,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,55</t>
+          <t>7,98; 12,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,37</t>
+          <t>2,72; 7,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,74; 23,49</t>
+          <t>8,79; 12,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,68</t>
+          <t>7,51; 10,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,74</t>
+          <t>3,81; 6,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,13</t>
+          <t>9,7; 12,93</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>31,36; 57,97</t>
+          <t>31,42; 59,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19,65; 44,51</t>
+          <t>20,11; 45,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23,44; 77,44</t>
+          <t>54,61; 86,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,13; 43,69</t>
+          <t>25,46; 43,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,55; 25,51</t>
+          <t>8,66; 25,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,86; 79,74</t>
+          <t>28,39; 44,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,29; 46,5</t>
+          <t>31,01; 46,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14,9; 29,39</t>
+          <t>15,58; 29,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>34,48; 72,37</t>
+          <t>39,77; 56,61</t>
         </is>
       </c>
     </row>
